--- a/reports/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/For The Week Ending (Actual)_Visits.xlsx
@@ -31,13 +31,13 @@
     <t>Purgatory</t>
   </si>
   <si>
+    <t>Purgatory Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Passes</t>
   </si>
   <si>
     <t>Purgatory Comp Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Tickets</t>
   </si>
 </sst>
 </file>
@@ -431,7 +431,7 @@
         <v>45992</v>
       </c>
       <c r="C2" s="2">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,7 +445,7 @@
         <v>45992</v>
       </c>
       <c r="C3" s="2">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -456,13 +456,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45993</v>
+        <v>45992</v>
       </c>
       <c r="C4" s="2">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,7 +473,7 @@
         <v>45993</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -487,10 +487,10 @@
         <v>45992</v>
       </c>
       <c r="C6" s="2">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -498,13 +498,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,10 +515,10 @@
         <v>45993</v>
       </c>
       <c r="C8" s="2">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,7 +532,7 @@
         <v>200</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,7 +546,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,10 +557,10 @@
         <v>45992</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,7 +571,7 @@
         <v>45993</v>
       </c>
       <c r="C12" s="2">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -585,10 +585,10 @@
         <v>45993</v>
       </c>
       <c r="C13" s="2">
-        <v>183</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/For The Week Ending (Actual)_Visits.xlsx
@@ -473,7 +473,7 @@
         <v>45992</v>
       </c>
       <c r="C5" s="2">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>6</v>
@@ -487,10 +487,10 @@
         <v>45993</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -498,13 +498,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="C7" s="2">
-        <v>50</v>
+        <v>183</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,7 +515,7 @@
         <v>45992</v>
       </c>
       <c r="C8" s="2">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -526,13 +526,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -540,13 +540,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45993</v>
+        <v>45992</v>
       </c>
       <c r="C10" s="2">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -554,10 +554,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45993</v>
+        <v>45992</v>
       </c>
       <c r="C11" s="2">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>6</v>
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -582,10 +582,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45993</v>
+        <v>45992</v>
       </c>
       <c r="C13" s="2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>7</v>

--- a/reports/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/For The Week Ending (Actual)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="8">
   <si>
     <t>Resort</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -428,10 +428,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45992</v>
+        <v>45999</v>
       </c>
       <c r="C2" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -442,10 +442,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="C3" s="2">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -456,10 +456,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="C4" s="2">
-        <v>2</v>
+        <v>358</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -470,13 +470,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45992</v>
+        <v>45999</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -484,13 +484,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="C6" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -498,13 +498,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="C7" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -512,10 +512,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -526,13 +526,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="C9" s="2">
-        <v>66</v>
+        <v>322</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -540,13 +540,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="C10" s="2">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -554,41 +554,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="C11" s="2">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="2">
-        <v>45993</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="2">
-        <v>45992</v>
-      </c>
-      <c r="C13" s="2">
-        <v>50</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/For The Week Ending (Actual)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,16 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
-  </si>
-  <si>
-    <t>Purgatory Comp Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Passes</t>
-  </si>
-  <si>
-    <t>Purgatory Tickets</t>
+    <t>Snowbowl</t>
+  </si>
+  <si>
+    <t>Snowbowl Passes</t>
+  </si>
+  <si>
+    <t>Snowbowl Comp Tickets</t>
+  </si>
+  <si>
+    <t>Snowbowl Tickets</t>
+  </si>
+  <si>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -400,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -431,7 +434,7 @@
         <v>45999</v>
       </c>
       <c r="C2" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,10 +448,10 @@
         <v>45999</v>
       </c>
       <c r="C3" s="2">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,10 +462,10 @@
         <v>45999</v>
       </c>
       <c r="C4" s="2">
-        <v>358</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,10 +476,10 @@
         <v>45999</v>
       </c>
       <c r="C5" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,10 +490,10 @@
         <v>45999</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -498,10 +501,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C7" s="2">
-        <v>21</v>
+        <v>718</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -512,13 +515,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C8" s="2">
-        <v>82</v>
+        <v>1059</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -526,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C9" s="2">
-        <v>322</v>
+        <v>97</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -540,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C10" s="2">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,10 +560,122 @@
         <v>46000</v>
       </c>
       <c r="C11" s="2">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C12" s="2">
         <v>2</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C13" s="2">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C14" s="2">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C15" s="2">
+        <v>85</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C16" s="2">
+        <v>79</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C17" s="2">
+        <v>570</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C18" s="2">
+        <v>918</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C19" s="2">
+        <v>53</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/For The Week Ending (Actual)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="8">
   <si>
     <t>Resort</t>
   </si>
@@ -28,19 +28,16 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Snowbowl</t>
-  </si>
-  <si>
-    <t>Snowbowl Passes</t>
-  </si>
-  <si>
-    <t>Snowbowl Comp Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Uplift Tickets</t>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>Purgatory Passes</t>
+  </si>
+  <si>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
+    <t>Purgatory Tickets</t>
   </si>
 </sst>
 </file>
@@ -403,13 +400,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -431,7 +428,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C2" s="2">
         <v>2</v>
@@ -445,13 +442,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C3" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,10 +456,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C4" s="2">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,10 +473,10 @@
         <v>45999</v>
       </c>
       <c r="C5" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,7 +487,7 @@
         <v>45999</v>
       </c>
       <c r="C6" s="2">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -501,13 +498,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C7" s="2">
-        <v>718</v>
+        <v>118</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,10 +515,10 @@
         <v>45999</v>
       </c>
       <c r="C8" s="2">
-        <v>1059</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,10 +529,10 @@
         <v>45999</v>
       </c>
       <c r="C9" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,10 +540,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>322</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -557,125 +554,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C11" s="2">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="2">
-        <v>46000</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="2">
-        <v>46000</v>
-      </c>
-      <c r="C13" s="2">
-        <v>7</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="2">
-        <v>46000</v>
-      </c>
-      <c r="C14" s="2">
-        <v>7</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="2">
-        <v>46000</v>
-      </c>
-      <c r="C15" s="2">
-        <v>85</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="2">
-        <v>46000</v>
-      </c>
-      <c r="C16" s="2">
-        <v>79</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="2">
-        <v>46000</v>
-      </c>
-      <c r="C17" s="2">
-        <v>570</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="2">
-        <v>46000</v>
-      </c>
-      <c r="C18" s="2">
-        <v>918</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="2">
-        <v>46000</v>
-      </c>
-      <c r="C19" s="2">
-        <v>53</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/For The Week Ending (Actual)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="8">
   <si>
     <t>Resort</t>
   </si>
@@ -31,10 +31,10 @@
     <t>Purgatory</t>
   </si>
   <si>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Passes</t>
-  </si>
-  <si>
-    <t>Purgatory Comp Tickets</t>
   </si>
   <si>
     <t>Purgatory Tickets</t>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -428,10 +428,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C2" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,7 +445,7 @@
         <v>46000</v>
       </c>
       <c r="C3" s="2">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -456,13 +456,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C4" s="2">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -470,13 +470,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C5" s="2">
-        <v>358</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,10 +487,10 @@
         <v>45999</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>358</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -498,13 +498,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C7" s="2">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -512,13 +512,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C8" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,10 +529,10 @@
         <v>45999</v>
       </c>
       <c r="C9" s="2">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -540,10 +540,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C10" s="2">
-        <v>322</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -554,13 +554,97 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C12" s="2">
+        <v>398</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C13" s="2">
+        <v>134</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2">
         <v>45999</v>
       </c>
-      <c r="C11" s="2">
-        <v>106</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C14" s="2">
+        <v>115</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C15" s="2">
+        <v>322</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C16" s="2">
+        <v>21</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C17" s="2">
+        <v>101</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/For The Week Ending (Actual)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,16 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Snowbowl Tickets</t>
+  </si>
+  <si>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -400,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -428,10 +431,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C2" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -442,13 +445,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C3" s="2">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,7 +462,7 @@
         <v>46001</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -470,13 +473,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>1059</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -484,10 +487,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C6" s="2">
-        <v>358</v>
+        <v>85</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -501,7 +504,7 @@
         <v>45999</v>
       </c>
       <c r="C7" s="2">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
@@ -512,13 +515,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C8" s="2">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -526,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C9" s="2">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,10 +546,10 @@
         <v>46001</v>
       </c>
       <c r="C10" s="2">
-        <v>25</v>
+        <v>1005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -554,13 +557,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -568,13 +571,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="C12" s="2">
-        <v>398</v>
+        <v>97</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -582,13 +585,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C13" s="2">
-        <v>134</v>
+        <v>570</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -596,13 +599,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C14" s="2">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -610,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C15" s="2">
-        <v>322</v>
+        <v>718</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -624,10 +627,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C16" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -638,13 +641,181 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C17" s="2">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C18" s="2">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C19" s="2">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C20" s="2">
+        <v>79</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C21" s="2">
+        <v>87</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C23" s="2">
+        <v>7</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C24" s="2">
+        <v>53</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>97</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C26" s="2">
+        <v>725</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C27" s="2">
+        <v>66</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C29" s="2">
+        <v>913</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/For The Week Ending (Actual)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,16 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Snowbowl Comp Tickets</t>
+  </si>
+  <si>
+    <t>Snowbowl Tickets</t>
   </si>
 </sst>
 </file>
@@ -400,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -428,10 +431,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C2" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -442,13 +445,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="C3" s="2">
-        <v>398</v>
+        <v>97</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -456,13 +459,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C4" s="2">
-        <v>134</v>
+        <v>570</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -470,10 +473,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C5" s="2">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -484,10 +487,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="C6" s="2">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>7</v>
@@ -498,10 +501,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C7" s="2">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -512,10 +515,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C8" s="2">
-        <v>358</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -526,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C9" s="2">
-        <v>4</v>
+        <v>1005</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -540,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C10" s="2">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,7 +560,7 @@
         <v>46002</v>
       </c>
       <c r="C11" s="2">
-        <v>321</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -568,10 +571,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C12" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>7</v>
@@ -582,10 +585,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="C13" s="2">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -596,13 +599,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="C14" s="2">
-        <v>174</v>
+        <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -610,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C15" s="2">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -624,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C16" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -638,10 +641,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C17" s="2">
-        <v>322</v>
+        <v>725</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -652,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>46002</v>
+        <v>45999</v>
       </c>
       <c r="C18" s="2">
-        <v>5</v>
+        <v>1058</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,10 +672,10 @@
         <v>46000</v>
       </c>
       <c r="C19" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -680,10 +683,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -694,13 +697,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="C21" s="2">
-        <v>1</v>
+        <v>1083</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -708,13 +711,237 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C22" s="2">
+        <v>718</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C24" s="2">
+        <v>7</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C26" s="2">
+        <v>66</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C27" s="2">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C28" s="2">
+        <v>913</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="2">
         <v>46002</v>
       </c>
-      <c r="C22" s="2">
-        <v>45</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="C29" s="2">
+        <v>79</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C30" s="2">
+        <v>2</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C31" s="2">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C32" s="2">
+        <v>80</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46002</v>
+      </c>
+      <c r="C33" s="2">
+        <v>82</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C34" s="2">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C35" s="2">
+        <v>79</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C36" s="2">
+        <v>87</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46002</v>
+      </c>
+      <c r="C37" s="2">
+        <v>11</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46002</v>
+      </c>
+      <c r="C38" s="2">
+        <v>741</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/For The Week Ending (Actual)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,19 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Snowbowl</t>
+    <t>Purgatory</t>
   </si>
   <si>
-    <t>Snowbowl Passes</t>
+    <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Snowbowl Uplift Tickets</t>
+    <t>Purgatory Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Comp Tickets</t>
+    <t>Purgatory Comp Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Tickets</t>
+    <t>Purgatory Coaster</t>
   </si>
 </sst>
 </file>
@@ -403,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -434,7 +434,7 @@
         <v>45999</v>
       </c>
       <c r="C2" s="2">
-        <v>7</v>
+        <v>358</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>45999</v>
       </c>
       <c r="C3" s="2">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -462,10 +462,10 @@
         <v>46000</v>
       </c>
       <c r="C4" s="2">
-        <v>570</v>
+        <v>118</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,10 +473,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>321</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -487,13 +487,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="C6" s="2">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,10 +501,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>46001</v>
+        <v>46004</v>
       </c>
       <c r="C7" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -515,13 +515,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>46001</v>
+        <v>46005</v>
       </c>
       <c r="C9" s="2">
-        <v>1005</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,10 +543,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>46002</v>
+        <v>46005</v>
       </c>
       <c r="C10" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -557,10 +557,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -571,13 +571,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C12" s="2">
-        <v>91</v>
+        <v>398</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,13 +585,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -599,10 +599,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C14" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -613,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>46000</v>
+        <v>46004</v>
       </c>
       <c r="C15" s="2">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -627,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>46001</v>
+        <v>46004</v>
       </c>
       <c r="C16" s="2">
-        <v>97</v>
+        <v>447</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,10 +641,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C17" s="2">
-        <v>725</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -655,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45999</v>
+        <v>46004</v>
       </c>
       <c r="C18" s="2">
-        <v>1058</v>
+        <v>1130</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,13 +669,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>46000</v>
+        <v>46004</v>
       </c>
       <c r="C19" s="2">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -683,13 +683,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="C20" s="2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,13 +697,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C21" s="2">
-        <v>1083</v>
+        <v>101</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45999</v>
+        <v>46002</v>
       </c>
       <c r="C22" s="2">
-        <v>718</v>
+        <v>174</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -725,13 +725,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>46000</v>
+        <v>46004</v>
       </c>
       <c r="C24" s="2">
-        <v>7</v>
+        <v>248</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,13 +753,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>46001</v>
+        <v>46005</v>
       </c>
       <c r="C25" s="2">
-        <v>10</v>
+        <v>332</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,10 +767,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C26" s="2">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -781,10 +781,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C27" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -795,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C28" s="2">
-        <v>913</v>
+        <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +812,10 @@
         <v>46002</v>
       </c>
       <c r="C29" s="2">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -823,10 +823,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C30" s="2">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -837,10 +837,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C31" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -851,13 +851,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>46001</v>
+        <v>46004</v>
       </c>
       <c r="C32" s="2">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -865,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>46002</v>
+        <v>46005</v>
       </c>
       <c r="C33" s="2">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45999</v>
+        <v>46005</v>
       </c>
       <c r="C34" s="2">
-        <v>9</v>
+        <v>124</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -893,13 +893,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>46000</v>
+        <v>46005</v>
       </c>
       <c r="C35" s="2">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,13 +907,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="C36" s="2">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,13 +921,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C37" s="2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,9 +938,163 @@
         <v>46002</v>
       </c>
       <c r="C38" s="2">
-        <v>741</v>
+        <v>93</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46004</v>
+      </c>
+      <c r="C39" s="2">
+        <v>2</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46004</v>
+      </c>
+      <c r="C40" s="2">
+        <v>99</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46005</v>
+      </c>
+      <c r="C41" s="2">
+        <v>105</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46005</v>
+      </c>
+      <c r="C42" s="2">
+        <v>925</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C43" s="2">
+        <v>115</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C44" s="2">
+        <v>322</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46002</v>
+      </c>
+      <c r="C45" s="2">
+        <v>5</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46003</v>
+      </c>
+      <c r="C46" s="2">
+        <v>538</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46004</v>
+      </c>
+      <c r="C47" s="2">
+        <v>132</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46005</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46005</v>
+      </c>
+      <c r="C49" s="2">
+        <v>13</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/reports/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/For The Week Ending (Actual)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,19 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Tickets</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -403,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -434,7 +434,7 @@
         <v>45999</v>
       </c>
       <c r="C2" s="2">
-        <v>358</v>
+        <v>1058</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,13 +445,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C3" s="2">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,13 +459,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C4" s="2">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,7 +476,7 @@
         <v>46002</v>
       </c>
       <c r="C5" s="2">
-        <v>321</v>
+        <v>1080</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -490,7 +490,7 @@
         <v>46003</v>
       </c>
       <c r="C6" s="2">
-        <v>213</v>
+        <v>133</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -501,13 +501,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>46004</v>
+        <v>46005</v>
       </c>
       <c r="C7" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,13 +515,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45999</v>
+        <v>46005</v>
       </c>
       <c r="C8" s="2">
-        <v>19</v>
+        <v>1548</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C9" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>46005</v>
+        <v>46000</v>
       </c>
       <c r="C10" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>46000</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,10 +574,10 @@
         <v>46001</v>
       </c>
       <c r="C12" s="2">
-        <v>398</v>
+        <v>97</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,10 +588,10 @@
         <v>46001</v>
       </c>
       <c r="C13" s="2">
-        <v>134</v>
+        <v>725</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,10 +602,10 @@
         <v>46003</v>
       </c>
       <c r="C14" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -613,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>46004</v>
+        <v>46003</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,10 +630,10 @@
         <v>46004</v>
       </c>
       <c r="C16" s="2">
-        <v>447</v>
+        <v>70</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,13 +641,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>46003</v>
+        <v>46004</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>847</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -655,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>46004</v>
+        <v>46005</v>
       </c>
       <c r="C18" s="2">
-        <v>1130</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,13 +669,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>46004</v>
+        <v>45999</v>
       </c>
       <c r="C19" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -683,13 +683,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C20" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,13 +697,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C21" s="2">
-        <v>101</v>
+        <v>570</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C22" s="2">
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,7 +728,7 @@
         <v>46003</v>
       </c>
       <c r="C23" s="2">
-        <v>27</v>
+        <v>997</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>7</v>
@@ -742,10 +742,10 @@
         <v>46004</v>
       </c>
       <c r="C24" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,13 +753,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C25" s="2">
-        <v>332</v>
+        <v>66</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,10 +770,10 @@
         <v>46000</v>
       </c>
       <c r="C26" s="2">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -781,10 +781,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C27" s="2">
-        <v>1</v>
+        <v>913</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -795,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="C28" s="2">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -809,10 +809,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C29" s="2">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>7</v>
@@ -826,7 +826,7 @@
         <v>46003</v>
       </c>
       <c r="C30" s="2">
-        <v>94</v>
+        <v>1104</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -837,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>46003</v>
+        <v>46004</v>
       </c>
       <c r="C31" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,10 +854,10 @@
         <v>46004</v>
       </c>
       <c r="C32" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,10 +868,10 @@
         <v>46005</v>
       </c>
       <c r="C33" s="2">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>46005</v>
+        <v>46000</v>
       </c>
       <c r="C34" s="2">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -893,10 +893,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>46005</v>
+        <v>46001</v>
       </c>
       <c r="C35" s="2">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>7</v>
@@ -907,13 +907,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C36" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,13 +921,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="C37" s="2">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -935,13 +935,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C38" s="2">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,10 +952,10 @@
         <v>46004</v>
       </c>
       <c r="C39" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,10 +966,10 @@
         <v>46004</v>
       </c>
       <c r="C40" s="2">
-        <v>99</v>
+        <v>1591</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,10 +980,10 @@
         <v>46005</v>
       </c>
       <c r="C41" s="2">
-        <v>105</v>
+        <v>339</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -991,13 +991,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C42" s="2">
-        <v>925</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1005,13 +1005,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="C43" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1019,13 +1019,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C44" s="2">
-        <v>322</v>
+        <v>87</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,10 +1036,10 @@
         <v>46002</v>
       </c>
       <c r="C45" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1047,13 +1047,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="C46" s="2">
-        <v>538</v>
+        <v>741</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1061,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>46004</v>
+        <v>46003</v>
       </c>
       <c r="C47" s="2">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1075,13 +1075,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>46005</v>
+        <v>46004</v>
       </c>
       <c r="C48" s="2">
-        <v>1</v>
+        <v>417</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,10 +1092,276 @@
         <v>46005</v>
       </c>
       <c r="C49" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46005</v>
+      </c>
+      <c r="C50" s="2">
+        <v>993</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C51" s="2">
+        <v>718</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C53" s="2">
+        <v>7</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C54" s="2">
+        <v>10</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46003</v>
+      </c>
+      <c r="C55" s="2">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="2">
+        <v>45999</v>
+      </c>
+      <c r="C56" s="2">
+        <v>77</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C57" s="2">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46002</v>
+      </c>
+      <c r="C60" s="2">
+        <v>4</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46002</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46002</v>
+      </c>
+      <c r="C62" s="2">
+        <v>91</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46003</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46004</v>
+      </c>
+      <c r="C64" s="2">
+        <v>5</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46005</v>
+      </c>
+      <c r="C65" s="2">
+        <v>2</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46005</v>
+      </c>
+      <c r="C66" s="2">
+        <v>2</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46005</v>
+      </c>
+      <c r="C67" s="2">
+        <v>3</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46005</v>
+      </c>
+      <c r="C68" s="2">
+        <v>187</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
